--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0020.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0020.xlsx
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Branch of Tacetite Weaponry, Huaxu Academy</t>
+          <t>Branch of Tacetite Vũ khíry, Huaxu Academy</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Internal Security Agency</t>
+          <t>Cơ quan An ninh Nội bộ</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Ministry of Sentinel Affairs</t>
+          <t>Bộ Sự Vụ Cảnh Vệ</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Mindsight</t>
+          <t>Thị giác tâm linh</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Paradimensional Tacet Field</t>
+          <t>Tổ Tacet Siêu Không Gian</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Grand Marshal</t>
+          <t>Đại Nguyên Soái</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Mingting</t>
+          <t>Minh Đình</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Ministry of War</t>
+          <t>Bộ Chiến Tranh</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Censorate</t>
+          <t>Cơ Quan Giám Sát</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Fenrico the First</t>
+          <t>Fenrico Đệ Nhất</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Land Huyền Phương</t>
+          <t>Vùng Đất Huyền Phương</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Voidworm</t>
+          <t>Giun Voidworm</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Infirmary</t>
+          <t>Phòng Y Tế</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Frequency Cassette Recorder</t>
+          <t>Máy Ghi Âm Tần Số</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Synchronist</t>
+          <t>Đồng Bộ Giả</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Reactor Drive</t>
+          <t>Bộ Truyền Động Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Starward Riseway</t>
+          <t>Đại Lộ Sao Chổi</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Greatsword</t>
+          <t>Đại Kiếm</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Voidmatter Barrier</t>
+          <t>Rào Cản Vật Chất Hư Không</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Roya Tribe</t>
+          <t>Bộ Lạc Roya</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>New Solar Ceremony</t>
+          <t>Lễ Hội Mặt Trời Mới</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>The Heliodic Six</t>
+          <t>Lục Hạo Nhật</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Exoswarm Material</t>
+          <t>Vật liệu Exoswarm</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Shepherd</t>
+          <t>Người Chăn Cừu</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Solistrees</t>
+          <t>Cây Solis</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Rite of Return</t>
+          <t>Nghi Thức Hồi Quy</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Void Storm</t>
+          <t>Bão Hư Không</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>Săn mồi</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Dark Tide Creation</t>
+          <t>Sáng Tạo Thủy Triều Bóng Tối</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Earthrend Wedge</t>
+          <t>Nêm Đất Nứt</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Canyons</t>
+          <t>Những hẻm núi</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Sacred Flame</t>
+          <t>Lửa Thiêng</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Holmleaf Medal</t>
+          <t>Huy Chương Holmleaf</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Anchor Stone</t>
+          <t>Đá Mỏ Neo</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Anchor Obelisk</t>
+          <t>Trụ Điểm Neo</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Wastelands</t>
+          <t>Vùng Hoang Mạc</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Hollow Figure</t>
+          <t>Hình Nhân Rỗng</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Waystone</t>
+          <t>Đá Dẫn Đường</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Echo-Type Combat Machine</t>
+          <t>Máy Chiến Đấu Loại Echo</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Glacio-Type Combat Machine</t>
+          <t>Cỗ Máy Chiến Đấu Loại Glacio</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Fusion-Type Combat Machine</t>
+          <t>Cỗ Máy Chiến Đấu Loại Fusion</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Aero-Type Combat Machine</t>
+          <t>Cỗ Máy Chiến Đấu Loại Aero</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Electro-Type Combat Machine</t>
+          <t>Cỗ Máy Chiến Đấu Điện Loại</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Lucky Coin</t>
+          <t>Đồng Xu May Mắn</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>KU-Money's Shop</t>
+          <t>Cửa hàng KU-Money</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Silent Lightning</t>
+          <t>Tia Chớp Vô Thanh</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Silver Bullet</t>
+          <t>Đạn Bạc</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Saturation Fire</t>
+          <t>Lửa Bão Hòa</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Lõi</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>DMG Enhancement</t>
+          <t>Tăng Sát Thương</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Enhancement Field</t>
+          <t>Trường Nâng Cấp</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Hunting Trap</t>
+          <t>Bẫy Săn</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Etheric Sea</t>
+          <t>Biển Nguyên Tố</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Stridergate</t>
+          <t>Cổng Bước Chân</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Fluctuating Voidmatter Levels</t>
+          <t>Mức Độ Vật Chất Hư Không Dao Động</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Mô-đun Adapter</t>
+          <t>Bộ chuyển đổi Mô-đun</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Snowfluff Seal</t>
+          <t>Ấn Chương Bông Tuyết</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Ichor</t>
+          <t>Dịch Huyết</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Novialle Regenerative Group</t>
+          <t>Tập Đoàn Tái Sinh Novialle</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Golden Anthem</t>
+          <t>Khúc Ca Hoàng Kim</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Anniversary Cake</t>
+          <t>Bánh kỷ niệm</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Solaris Trở Lại Lần Hai</t>
+          <t>Sự Trở Lại Của Solaris</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Khối Lập Phương</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hang Discipline</t>
+          <t>Chamber of Discipline</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Kênh dẫn</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Ghost Hounds</t>
+          <t>Bầy Ma Sói</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>The Golden Bough</t>
+          <t>Cành Cây Vàng</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Celestial Steed</t>
+          <t>Thiên Mã</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Melody</t>
+          <t>Giai điệu</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Zenith Windblade</t>
+          <t>Kiếm Gió Zenith</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Sanguine Wheel</t>
+          <t>Bánh Xe Huyết</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Glittering Ray</t>
+          <t>Tia Sáng Lấp Lánh</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Phaser</t>
+          <t>Bộ Điều Pha</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Breeze Breaker</t>
+          <t>Kẻ Phá Gió</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Ashen Oath</t>
+          <t>Lời Thề Tro Tàn</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Waxing Moon</t>
+          <t>Trăng Lưỡi Liềm</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Zephyr Symphony</t>
+          <t>Bản Giao Hưởng Zephyr</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Blazing Star</t>
+          <t>Ngôi Sao Rực Lửa</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Rampant Fire</t>
+          <t>Lửa Hoang</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Feilian Shock</t>
+          <t>Sốc Feilian</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Explosive Omen</t>
+          <t>Điềm Báo Nổ</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Bullet Weapon</t>
+          <t>Vũ khí đạn đạo</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Summon Weapon</t>
+          <t>Triệu hồi Vũ Khí</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Beam Weapon</t>
+          <t>Vũ Khí Tia</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Morph Weapon</t>
+          <t>Vũ Khí Hóa Hình</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Synergistic Evo</t>
+          <t>Tiến Hóa Cộng Hưởng</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>New Solar Celebration</t>
+          <t>Lễ Hội Mặt Trời Mới</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Academy's Dark Side</t>
+          <t>Mặt Tối Của Học Viện</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Reflection</t>
+          <t>Phản Chiếu</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Minerva's Treasure</t>
+          <t>Kho báu của Minerva</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Incarnation</t>
+          <t>Hóa Thân</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Incandescence</t>
+          <t>Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>True Sight</t>
+          <t>Thị Lực Chân Thật</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Enflamement</t>
+          <t>Lửa Thiêu Đốt</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Photosynthesis Energy</t>
+          <t>Năng Lượng Quang Hợp</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Ring of Mirrors</t>
+          <t>Nhẫn Gương Phản Chiếu</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
